--- a/Zoomlion/ZS Série 2022.xlsx
+++ b/Zoomlion/ZS Série 2022.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,32 +429,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Material No.</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Item and Spec</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
@@ -2466,7 +2478,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0808; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS0808; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2608,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2634,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3816,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3842,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3894,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3972,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4292,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4630,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4656,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5930,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6090,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6116,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6146,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6176,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6202,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6228,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0808</t>
+          <t>ZS0808; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6280,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6306,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6332,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6358,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6410,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6436,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6462,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6488,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6514,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6540,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6566,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6592,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6618,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6644,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6670,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6696,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6722,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6748,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6774,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6800,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6826,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0808; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS0808; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6852,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6878,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6904,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6930,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6982,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -6996,7 +7008,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7034,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7060,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7086,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7112,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7138,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7152,7 +7164,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7190,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7216,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7242,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7294,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7320,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7346,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7372,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7398,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7554,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7580,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7606,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7632,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7658,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7684,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7710,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7766,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7792,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7818,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7844,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7870,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7896,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7922,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7948,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7974,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -7988,7 +8000,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8026,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8052,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8428,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8660,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8690,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0808</t>
+          <t>ZS0808; ZS0607</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8768,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>ZS0608; ZS1012</t>
+          <t>ZS1012; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8872,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8898,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012</t>
+          <t>ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8924,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012</t>
+          <t>ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8950,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012</t>
+          <t>ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9188,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>ZS1012; ZS1414</t>
+          <t>ZS1414; ZS1012</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9214,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012</t>
+          <t>ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9240,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9266,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9296,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9322,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9348,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9374,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9400,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9426,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9452,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9478,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9634,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9660,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9686,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9712,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9738,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9842,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9868,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9920,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9946,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9972,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9998,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10024,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10050,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10076,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10102,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10154,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0608; ZS0808</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10180,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10206,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10232,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10258,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10284,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10310,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10336,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10362,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10388,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10414,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10466,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1212</t>
+          <t>ZS1212; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10492,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10518,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10544,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>ZS0808; ZS0812; ZS1212</t>
+          <t>ZS1212; ZS0812; ZS0808</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10600,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>ZS0808; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0808</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10652,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10678,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10704,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10730,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10756,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10782,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10808,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1012; ZS1212; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10834,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10860,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10886,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10912,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10938,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012</t>
+          <t>ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10968,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS0812</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10998,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11028,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11054,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11084,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11114,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11140,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11166,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11192,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11218,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11244,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11270,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11296,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11322,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0608; ZS0808</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11348,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11374,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11400,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11426,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11478,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11504,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11530,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -11544,7 +11556,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11582,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11596,7 +11608,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11634,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11660,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11686,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11712,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11738,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11764,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11790,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11816,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11868,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11894,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11920,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11964,7 +11976,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -11990,7 +12002,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12054,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12080,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12132,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12236,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12262,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>ZS0808; ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812; ZS0808</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12494,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -12508,7 +12520,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12546,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12572,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12598,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12624,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12676,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12754,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12784,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12840,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12918,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12944,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12970,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12996,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13542,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14372,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14398,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -14412,7 +14424,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14450,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -14520,7 +14532,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812</t>
+          <t>ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -14550,7 +14562,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14760,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14786,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14812,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -14826,7 +14838,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -14878,7 +14890,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14994,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15020,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15046,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15072,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15098,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15124,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15154,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -15172,7 +15184,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15604,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15814,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15960,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -15974,7 +15986,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16060,7 +16072,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16098,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16124,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16150,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16176,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16202,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212</t>
+          <t>ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16306,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16358,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16548,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16562,7 +16574,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16626,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16652,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808</t>
         </is>
       </c>
     </row>
@@ -16666,7 +16678,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16696,7 +16708,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0808; ZS0608; ZS0812; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16738,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16764,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -16782,7 +16794,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0607; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -16808,7 +16820,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16846,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0808; ZS0608; ZS0812; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16860,7 +16872,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16898,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16912,7 +16924,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -16964,7 +16976,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -16990,7 +17002,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17054,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -17068,7 +17080,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -17150,7 +17162,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -17176,7 +17188,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17214,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17240,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17266,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -17280,7 +17292,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -17426,7 +17438,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -17504,7 +17516,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17542,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17620,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17646,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17702,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -17742,7 +17754,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17780,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -17828,7 +17840,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17956,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -18030,7 +18042,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18094,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0607; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18120,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -18242,7 +18254,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0407</t>
         </is>
       </c>
     </row>
@@ -18268,7 +18280,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -18458,7 +18470,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18500,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012</t>
+          <t>ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -18548,7 +18560,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18590,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -18608,7 +18620,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -18668,7 +18680,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -18698,7 +18710,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -18728,7 +18740,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -18758,7 +18770,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -18788,7 +18800,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -18818,7 +18830,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -18848,7 +18860,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -18878,7 +18890,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -18998,7 +19010,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0407; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19028,7 +19040,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19070,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19088,7 +19100,7 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19208,7 +19220,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -19238,7 +19250,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19298,7 +19310,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -19328,7 +19340,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19418,7 +19430,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -19478,7 +19490,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -19538,7 +19550,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -19598,7 +19610,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -19628,7 +19640,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -19658,7 +19670,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -19688,7 +19700,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0607; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -19718,7 +19730,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0808; ZS0608; ZS0607; ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -19808,7 +19820,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19838,7 +19850,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -19898,7 +19910,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -19958,7 +19970,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0407; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -19988,7 +20000,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20030,7 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0607; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -20048,7 +20060,7 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20120,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20150,7 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20168,7 +20180,7 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20240,7 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0407; ZS0808; ZS0608; ZS0607; ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -20258,7 +20270,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0607; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -20288,7 +20300,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -20318,7 +20330,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20348,7 +20360,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20378,7 +20390,7 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20408,7 +20420,7 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20468,7 +20480,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -20498,7 +20510,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20630,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0407; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -20648,7 +20660,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20708,7 +20720,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0407; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -20738,7 +20750,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20768,7 +20780,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20798,7 +20810,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20828,7 +20840,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20900,7 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -20918,7 +20930,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20960,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0407; ZS0808; ZS0608; ZS0607; ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -20978,7 +20990,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21008,7 +21020,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21050,7 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0607; ZS0407; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -21068,7 +21080,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0407; ZS0808; ZS0608; ZS0607; ZS1414; ZS1212; ZS1012; ZS0812</t>
         </is>
       </c>
     </row>
@@ -21128,7 +21140,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21158,7 +21170,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21218,7 +21230,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21260,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21350,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0607; ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21380,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -21428,7 +21440,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21458,7 +21470,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -21548,7 +21560,7 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21608,7 +21620,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -21698,7 +21710,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21728,7 +21740,7 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21770,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21818,7 +21830,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -21848,7 +21860,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21878,7 +21890,7 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21908,7 +21920,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -21938,7 +21950,7 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -21968,7 +21980,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22040,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22070,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22088,7 +22100,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -22148,7 +22160,7 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22204,7 +22216,7 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22230,7 +22242,7 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -22256,7 +22268,7 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS0607; ZS0407; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22294,7 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22320,7 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22346,7 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22372,7 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -22386,7 +22398,7 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608</t>
         </is>
       </c>
     </row>
@@ -22490,7 +22502,7 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607</t>
+          <t>ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22594,7 +22606,7 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -22650,7 +22662,7 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808</t>
+          <t>ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -22676,7 +22688,7 @@
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22702,7 +22714,7 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -22754,7 +22766,7 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
@@ -22784,7 +22796,7 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -22810,7 +22822,7 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -22862,7 +22874,7 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -23312,7 +23324,7 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS0812; ZS1012; ZS1212; ZS1414; ZS0407; ZS0607; ZS0608; ZS0808</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23470,7 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0608; ZS0808; ZS0607</t>
         </is>
       </c>
     </row>
@@ -23484,7 +23496,7 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -23510,7 +23522,7 @@
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607</t>
         </is>
       </c>
     </row>
@@ -23562,7 +23574,7 @@
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>ZS0407; ZS0607; ZS0608; ZS0808; ZS0812; ZS1012; ZS1212; ZS1414</t>
+          <t>ZS1414; ZS1212; ZS1012; ZS0812; ZS0808; ZS0608; ZS0607; ZS0407</t>
         </is>
       </c>
     </row>
